--- a/resources/templates/standard/A6200-01.xlsx
+++ b/resources/templates/standard/A6200-01.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>분임조 등록카드</t>
   </si>
@@ -698,7 +701,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -706,7 +711,7 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
@@ -729,23 +734,23 @@
       <c r="AA1" s="2"/>
       <c r="AB1" s="2"/>
       <c r="AC1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD1" s="3"/>
       <c r="AE1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF1" s="4"/>
       <c r="AG1" s="4"/>
       <c r="AH1" s="4"/>
       <c r="AI1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ1" s="4"/>
       <c r="AK1" s="4"/>
       <c r="AL1" s="4"/>
       <c r="AM1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN1" s="4"/>
       <c r="AO1" s="4"/>
@@ -885,7 +890,7 @@
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -908,7 +913,7 @@
       <c r="T5" s="8"/>
       <c r="U5" s="8"/>
       <c r="V5" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W5" s="4"/>
       <c r="X5" s="4"/>
@@ -933,7 +938,7 @@
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -956,7 +961,7 @@
       <c r="T6" s="10"/>
       <c r="U6" s="10"/>
       <c r="V6" s="11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W6" s="11"/>
       <c r="X6" s="11"/>
@@ -981,7 +986,7 @@
     </row>
     <row r="7" ht="17.1" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" s="12"/>
       <c r="C7" s="12"/>
@@ -1004,7 +1009,7 @@
       <c r="T7" s="5"/>
       <c r="U7" s="5"/>
       <c r="V7" s="11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W7" s="11"/>
       <c r="X7" s="11"/>
@@ -1050,7 +1055,7 @@
       <c r="T8" s="5"/>
       <c r="U8" s="5"/>
       <c r="V8" s="11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W8" s="11"/>
       <c r="X8" s="11"/>
@@ -1075,7 +1080,7 @@
     </row>
     <row r="9" ht="23.25" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -1121,7 +1126,7 @@
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -1129,12 +1134,12 @@
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
       <c r="G10" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
       <c r="J10" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K10" s="11"/>
       <c r="L10" s="11"/>
@@ -1142,7 +1147,7 @@
       <c r="N10" s="11"/>
       <c r="O10" s="11"/>
       <c r="P10" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q10" s="11"/>
       <c r="R10" s="11"/>
@@ -1150,7 +1155,7 @@
       <c r="T10" s="11"/>
       <c r="U10" s="11"/>
       <c r="V10" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W10" s="11"/>
       <c r="X10" s="11"/>
@@ -1158,12 +1163,12 @@
       <c r="Z10" s="11"/>
       <c r="AA10" s="11"/>
       <c r="AB10" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC10" s="11"/>
       <c r="AD10" s="11"/>
       <c r="AE10" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF10" s="11"/>
       <c r="AG10" s="11"/>
@@ -1171,7 +1176,7 @@
       <c r="AI10" s="11"/>
       <c r="AJ10" s="11"/>
       <c r="AK10" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL10" s="11"/>
       <c r="AM10" s="11"/>
@@ -1533,7 +1538,7 @@
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" s="15"/>
       <c r="C19" s="15"/>
